--- a/erp-server/erp-server-file/src/main/resources/excel/workflow/processDefinition.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/workflow/processDefinition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="流程设计记录" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>流程定义ID</t>
   </si>
@@ -44,6 +44,9 @@
     <t>流程版本</t>
   </si>
   <si>
+    <t>禁用状态</t>
+  </si>
+  <si>
     <t>审核人设置</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t>{.processVersion}</t>
+  </si>
+  <si>
+    <t>{.disabledName}</t>
   </si>
   <si>
     <t>{.reviewSetting}</t>
@@ -582,7 +588,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1273,13 +1279,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="9" width="20" customWidth="1"/>
+    <col min="1" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:9">
+    <row r="1" ht="15" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1307,34 +1313,40 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
